--- a/Excel_Dashboard_Tutorial.xlsx
+++ b/Excel_Dashboard_Tutorial.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💼 D4 - Job Title" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📅 D5 - Tenure" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🧑‍💼 D6 - Employee" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🌟 Pro Tips &amp; Tricks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🐞 QA Dashboard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🌟 Pro Tips &amp; Tricks" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -223,8 +224,36 @@
       <color rgb="00E67E22"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00CF222E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="002EA44F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F6FEB"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00856404"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00CF222E"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -346,8 +375,38 @@
         <fgColor rgb="00FEF5E7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D1117"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CF222E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6FEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECEA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -413,11 +472,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -687,6 +760,55 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="30" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="30" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1235,9 +1357,24 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>📋  EXCEL SKILLS YOU WILL LEARN IN THIS TUTORIAL</t>
+      <c r="A11" s="97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="98" t="inlineStr">
+        <is>
+          <t>QA Dashboard</t>
+        </is>
+      </c>
+      <c r="C11" s="99" t="inlineStr">
+        <is>
+          <t>Bug tracking, test execution, tester scorecard, sprint health</t>
+        </is>
+      </c>
+      <c r="D11" s="99" t="inlineStr">
+        <is>
+          <t>Pie + Column + H-Bar + Stacked + Line x2</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1604,11 @@
       <c r="E26" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="32">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C12:E12"/>
@@ -1501,6 +1637,574 @@
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C25:E25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D35400"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>🌟  PRO EXCEL TIPS &amp; KEYBOARD SHORTCUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>⌨️  NAVIGATION SHORTCUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Shortcut / Tip</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>What it Does</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="70" t="inlineStr">
+        <is>
+          <t>Ctrl + Home</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>Go to cell A1 — the very beginning of the sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="71" t="inlineStr">
+        <is>
+          <t>Ctrl + End</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>Go to the last used cell in the sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>Ctrl + Arrow Keys</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>Jump to the last cell with data in any direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="71" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + End</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>Select from current cell to last used cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>Ctrl + Page Up/Down</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>Switch between worksheet tabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="71" t="inlineStr">
+        <is>
+          <t>F5 (Go To)</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>Navigate directly to any cell address or named range</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>📝  EDITING SHORTCUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>Shortcut / Tip</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>What it Does</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="72" t="inlineStr">
+        <is>
+          <t>Ctrl + Z / Y</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>Undo / Redo — your best friends!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="73" t="inlineStr">
+        <is>
+          <t>Ctrl + C / X / V</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>Copy / Cut / Paste</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="72" t="inlineStr">
+        <is>
+          <t>Ctrl + D</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>Fill Down — copy formula from cell above to selected range</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="73" t="inlineStr">
+        <is>
+          <t>Ctrl + R</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>Fill Right — copy formula from left cell to selected range</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="72" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>Enter edit mode in the active cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="73" t="inlineStr">
+        <is>
+          <t>Ctrl + Enter</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>Enter data in multiple selected cells at once</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="72" t="inlineStr">
+        <is>
+          <t>Alt + Enter</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>Add a new line WITHIN a cell (instead of moving to next cell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="73" t="inlineStr">
+        <is>
+          <t>Ctrl + ;</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>Insert today's date</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="72" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + ;</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>Insert current time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>🎨  FORMATTING SHORTCUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="45" t="inlineStr">
+        <is>
+          <t>Shortcut / Tip</t>
+        </is>
+      </c>
+      <c r="C25" s="45" t="inlineStr">
+        <is>
+          <t>What it Does</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="74" t="inlineStr">
+        <is>
+          <t>Ctrl + 1</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>Open Format Cells dialog (quickest way!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="75" t="inlineStr">
+        <is>
+          <t>Ctrl + B / I / U</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>Bold / Italic / Underline</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="74" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + $</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>Apply Currency format instantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="75" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + %</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>Apply Percentage format instantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="74" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + #</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>Apply Date format instantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="75" t="inlineStr">
+        <is>
+          <t>Alt + H + H</t>
+        </is>
+      </c>
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>Open cell background color picker</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="74" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + C/V</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>Copy / Paste formatting only (Format Painter via keyboard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="25" customHeight="1">
+      <c r="A34" s="59" t="inlineStr">
+        <is>
+          <t>📊  CHART TRICKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="76" t="inlineStr">
+        <is>
+          <t>Shortcut / Tip</t>
+        </is>
+      </c>
+      <c r="C35" s="76" t="inlineStr">
+        <is>
+          <t>What it Does</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="77" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>Create a chart on a NEW sheet from selected data instantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="78" t="inlineStr">
+        <is>
+          <t>Alt + F1</t>
+        </is>
+      </c>
+      <c r="C37" s="37" t="inlineStr">
+        <is>
+          <t>Create a chart EMBEDDED in the current sheet from selected data</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="77" t="inlineStr">
+        <is>
+          <t>Click chart + Delete</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>Delete a chart quickly</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="78" t="inlineStr">
+        <is>
+          <t>Ctrl + click bars</t>
+        </is>
+      </c>
+      <c r="C39" s="37" t="inlineStr">
+        <is>
+          <t>Select one specific bar/slice to format individually</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="77" t="inlineStr">
+        <is>
+          <t>Double-click axis</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>Open Format Axis panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="78" t="inlineStr">
+        <is>
+          <t>Right-click → Select Data</t>
+        </is>
+      </c>
+      <c r="C41" s="37" t="inlineStr">
+        <is>
+          <t>Change what data the chart uses</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>💡  DASHBOARD BEST PRACTICES</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="79" t="inlineStr">
+        <is>
+          <t>Shortcut / Tip</t>
+        </is>
+      </c>
+      <c r="C44" s="79" t="inlineStr">
+        <is>
+          <t>What it Does</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="80" t="inlineStr">
+        <is>
+          <t>Use consistent colors</t>
+        </is>
+      </c>
+      <c r="C45" s="33" t="inlineStr">
+        <is>
+          <t>Pick 2-3 main colors and stick to them throughout</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="81" t="inlineStr">
+        <is>
+          <t>Align everything</t>
+        </is>
+      </c>
+      <c r="C46" s="37" t="inlineStr">
+        <is>
+          <t>Charts and tables should align to cell grid (hold Alt while resizing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="80" t="inlineStr">
+        <is>
+          <t>Less is more</t>
+        </is>
+      </c>
+      <c r="C47" s="33" t="inlineStr">
+        <is>
+          <t>Don't add every possible chart — 4-6 visuals max per dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="81" t="inlineStr">
+        <is>
+          <t>Add a title section</t>
+        </is>
+      </c>
+      <c r="C48" s="37" t="inlineStr">
+        <is>
+          <t>Every dashboard needs a clear title + date/source information</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="80" t="inlineStr">
+        <is>
+          <t>Use named ranges</t>
+        </is>
+      </c>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>Name your key data ranges (Ctrl+F3) for cleaner formulas</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="81" t="inlineStr">
+        <is>
+          <t>Protect your summary sheets</t>
+        </is>
+      </c>
+      <c r="C50" s="37" t="inlineStr">
+        <is>
+          <t>Review tab → Protect Sheet so formula cells can't be broken</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="80" t="inlineStr">
+        <is>
+          <t>Test responsiveness</t>
+        </is>
+      </c>
+      <c r="C51" s="33" t="inlineStr">
+        <is>
+          <t>Click slicers/filters to verify all charts update correctly</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="81" t="inlineStr">
+        <is>
+          <t>Save as .xlsx</t>
+        </is>
+      </c>
+      <c r="C52" s="37" t="inlineStr">
+        <is>
+          <t>Always save as .xlsx to preserve charts, formatting &amp; macros</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="D4"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="D35"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="D44"/>
+    <mergeCell ref="D25"/>
+    <mergeCell ref="D13"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4442,6 +5146,10 @@
           <t>💡 TIP: AVERAGEIFS, MINIFS, and MAXIFS all follow the same pattern: (value_range, criteria_range1, criteria1, criteria_range2, criteria2). Master these and you can calculate almost any metric!</t>
         </is>
       </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="21" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="93" t="inlineStr">
@@ -4622,6 +5330,10 @@
           <t>💡 TIP: Use CONCATENATE or &amp; to combine text and numbers in KPI cards. Example: ="Total: "&amp;TEXT(SUM(G:G),"$#,##0") creates a formatted string like 'Total: $45,123,000'</t>
         </is>
       </c>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="21" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="63" t="inlineStr">
@@ -4769,6 +5481,10 @@
           <t>💡 TIP: To set the same size for multiple charts: Ctrl+click each chart → Format tab → enter exact Height and Width values. Professional dashboards use consistent chart sizes!</t>
         </is>
       </c>
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="21" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="59" t="inlineStr">
@@ -4918,6 +5634,10 @@
           <t>💡 TIP: Before sharing your dashboard: File → Print Preview to see how it looks on paper. Set Page Layout → Fit to 1 page wide to ensure it prints cleanly if needed.</t>
         </is>
       </c>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="21" t="n"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="90" t="inlineStr">
@@ -5150,566 +5870,1128 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00D35400"/>
+    <tabColor rgb="00CF222E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>🌟  PRO EXCEL TIPS &amp; KEYBOARD SHORTCUTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>⌨️  NAVIGATION SHORTCUTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>Shortcut / Tip</t>
-        </is>
-      </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>What it Does</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="70" t="inlineStr">
-        <is>
-          <t>Ctrl + Home</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>Go to cell A1 — the very beginning of the sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="71" t="inlineStr">
-        <is>
-          <t>Ctrl + End</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>Go to the last used cell in the sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="70" t="inlineStr">
-        <is>
-          <t>Ctrl + Arrow Keys</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="inlineStr">
-        <is>
-          <t>Jump to the last cell with data in any direction</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="71" t="inlineStr">
-        <is>
-          <t>Ctrl + Shift + End</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>Select from current cell to last used cell</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="70" t="inlineStr">
-        <is>
-          <t>Ctrl + Page Up/Down</t>
-        </is>
-      </c>
-      <c r="C9" s="33" t="inlineStr">
-        <is>
-          <t>Switch between worksheet tabs</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="71" t="inlineStr">
-        <is>
-          <t>F5 (Go To)</t>
-        </is>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>Navigate directly to any cell address or named range</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="38" t="inlineStr">
-        <is>
-          <t>📝  EDITING SHORTCUTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>Shortcut / Tip</t>
-        </is>
-      </c>
-      <c r="C13" s="39" t="inlineStr">
-        <is>
-          <t>What it Does</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="72" t="inlineStr">
-        <is>
-          <t>Ctrl + Z / Y</t>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="100" t="inlineStr">
+        <is>
+          <t>🐞  QA DASHBOARD — BUILDING A SOFTWARE QUALITY TRACKER IN EXCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="86" t="inlineStr">
+        <is>
+          <t>Learn to build a full QA dashboard: bug tracking, test execution, tester scorecards &amp; sprint health</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="101" t="inlineStr">
+        <is>
+          <t>🗂️  6 SHEETS IN THE QA_Dashboard.xlsx FILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="102" t="inlineStr">
+        <is>
+          <t>🎯 QA Dashboard</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="103" t="inlineStr">
+        <is>
+          <t>Main visual dashboard: 6 KPI cards, 6 charts, critical bug table</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="n"/>
+      <c r="E4" s="21" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="104" t="inlineStr">
+        <is>
+          <t>📋 Bug Tracker</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="105" t="inlineStr">
+        <is>
+          <t>200 sample bugs with severity, status, module, tester, days open</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="21" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="102" t="inlineStr">
+        <is>
+          <t>✅ Test Runs</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="103" t="inlineStr">
+        <is>
+          <t>Sprint-by-sprint test execution: passed, failed, blocked counts</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="21" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="104" t="inlineStr">
+        <is>
+          <t>📊 Chart Data</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="105" t="inlineStr">
+        <is>
+          <t>Calculated summaries feeding all 6 charts (never edit this!)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="21" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="102" t="inlineStr">
+        <is>
+          <t>🏆 Tester Scorecard</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="103" t="inlineStr">
+        <is>
+          <t>Ranked performance table with close rate + data bars</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="21" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="104" t="inlineStr">
+        <is>
+          <t>📅 Sprint Health</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="105" t="inlineStr">
+        <is>
+          <t>Sprint-level health score combining pass rate + DRE metric</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="21" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="106" t="inlineStr">
+        <is>
+          <t>PHASE 1: BUILD THE BUG TRACKER SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="107" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B11" s="107" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C11" s="107" t="inlineStr">
+        <is>
+          <t>Instructions</t>
+        </is>
+      </c>
+      <c r="D11" s="107" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="E11" s="107" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="108" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>Create Bug Tracker Sheet</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>Create a new sheet called 'Bug Tracker'
+Add headers in row 1:
+Bug ID | Title | Severity | Status | Module | Tester | Sprint | Created | Resolved | Days Open | Test Type | Environment</t>
+        </is>
+      </c>
+      <c r="D12" s="57" t="inlineStr"/>
+      <c r="E12" s="109" t="inlineStr">
+        <is>
+          <t>Headers ready ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="108" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="B13" s="52" t="inlineStr">
+        <is>
+          <t>Data Validation — Severity</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>Select column C (Severity)
+Data tab → Data Validation → Allow: List
+Source: Critical,High,Medium,Low
+Now only valid severities can be entered — no typos!</t>
+        </is>
+      </c>
+      <c r="D13" s="57" t="inlineStr"/>
+      <c r="E13" s="109" t="inlineStr">
+        <is>
+          <t>Dropdown list added ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="108" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="B14" s="52" t="inlineStr">
+        <is>
+          <t>Data Validation — Status</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>Undo / Redo — your best friends!</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="73" t="inlineStr">
-        <is>
-          <t>Ctrl + C / X / V</t>
+          <t>Select column D (Status)
+Data Validation → List
+Source: Open,In Progress,Fixed,Verified,Closed,Reopened
+This enforces consistent status values across the whole team</t>
+        </is>
+      </c>
+      <c r="D14" s="57" t="inlineStr"/>
+      <c r="E14" s="109" t="inlineStr">
+        <is>
+          <t>Status dropdown ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="108" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="B15" s="52" t="inlineStr">
+        <is>
+          <t>Auto-Calculate Days Open</t>
         </is>
       </c>
       <c r="C15" s="37" t="inlineStr">
         <is>
-          <t>Copy / Cut / Paste</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="72" t="inlineStr">
-        <is>
-          <t>Ctrl + D</t>
+          <t>In column J (Days Open):
+If bug is open: =TODAY()-H2  (today minus created date)
+If closed: =I2-H2  (resolved date minus created date)
+Use IF: =IF(D2="Closed",I2-H2,TODAY()-H2)</t>
+        </is>
+      </c>
+      <c r="D15" s="57">
+        <f>IF(D2="Closed",I2-H2,TODAY()-H2)</f>
+        <v/>
+      </c>
+      <c r="E15" s="109" t="inlineStr">
+        <is>
+          <t>Auto-calculates daily ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="108" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="B16" s="52" t="inlineStr">
+        <is>
+          <t>Color-Code Severity with Conditional Formatting</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>Fill Down — copy formula from cell above to selected range</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="73" t="inlineStr">
-        <is>
-          <t>Ctrl + R</t>
+          <t>Select column C → Home → Conditional Formatting → New Rule
+Rule 1: Cell = 'Critical' → Red fill, white text
+Rule 2: Cell = 'High'     → Orange fill
+Rule 3: Cell = 'Medium'   → Yellow fill
+Rule 4: Cell = 'Low'      → Green fill</t>
+        </is>
+      </c>
+      <c r="D16" s="57" t="inlineStr"/>
+      <c r="E16" s="109" t="inlineStr">
+        <is>
+          <t>Traffic light colors ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="108" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="B17" s="52" t="inlineStr">
+        <is>
+          <t>Filter &amp; Sort Bugs</t>
         </is>
       </c>
       <c r="C17" s="37" t="inlineStr">
         <is>
-          <t>Fill Right — copy formula from left cell to selected range</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="72" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="C18" s="33" t="inlineStr">
-        <is>
-          <t>Enter edit mode in the active cell</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="73" t="inlineStr">
-        <is>
-          <t>Ctrl + Enter</t>
-        </is>
-      </c>
-      <c r="C19" s="37" t="inlineStr">
-        <is>
-          <t>Enter data in multiple selected cells at once</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="72" t="inlineStr">
-        <is>
-          <t>Alt + Enter</t>
-        </is>
-      </c>
-      <c r="C20" s="33" t="inlineStr">
-        <is>
-          <t>Add a new line WITHIN a cell (instead of moving to next cell)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="73" t="inlineStr">
-        <is>
-          <t>Ctrl + ;</t>
+          <t>Click any header cell → Data tab → Filter (Ctrl+Shift+L)
+Now dropdown arrows appear on each column
+Click Severity dropdown → select 'Critical' → only critical bugs show
+This lets you focus on what matters most instantly!</t>
+        </is>
+      </c>
+      <c r="D17" s="57" t="inlineStr"/>
+      <c r="E17" s="109" t="inlineStr">
+        <is>
+          <t>Filtering enabled ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t>💡 TIP: Format your bug tracker as a Table (Ctrl+T) so new rows auto-inherit formulas, formatting, and filters. Name it 'BugTable' for clean formula references.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="110" t="inlineStr">
+        <is>
+          <t>PHASE 2: BUILD CHART DATA SUMMARY SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="108" t="inlineStr">
+        <is>
+          <t>Step 7</t>
+        </is>
+      </c>
+      <c r="B21" s="52" t="inlineStr">
+        <is>
+          <t>Count Bugs by Severity</t>
         </is>
       </c>
       <c r="C21" s="37" t="inlineStr">
         <is>
-          <t>Insert today's date</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="72" t="inlineStr">
-        <is>
-          <t>Ctrl + Shift + ;</t>
-        </is>
-      </c>
-      <c r="C22" s="33" t="inlineStr">
-        <is>
-          <t>Insert current time</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="44" t="inlineStr">
-        <is>
-          <t>🎨  FORMATTING SHORTCUTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="45" t="inlineStr">
-        <is>
-          <t>Shortcut / Tip</t>
-        </is>
-      </c>
-      <c r="C25" s="45" t="inlineStr">
-        <is>
-          <t>What it Does</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="74" t="inlineStr">
-        <is>
-          <t>Ctrl + 1</t>
-        </is>
-      </c>
-      <c r="C26" s="33" t="inlineStr">
-        <is>
-          <t>Open Format Cells dialog (quickest way!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="75" t="inlineStr">
-        <is>
-          <t>Ctrl + B / I / U</t>
-        </is>
-      </c>
-      <c r="C27" s="37" t="inlineStr">
-        <is>
-          <t>Bold / Italic / Underline</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="74" t="inlineStr">
-        <is>
-          <t>Ctrl + Shift + $</t>
-        </is>
-      </c>
-      <c r="C28" s="33" t="inlineStr">
-        <is>
-          <t>Apply Currency format instantly</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="75" t="inlineStr">
-        <is>
-          <t>Ctrl + Shift + %</t>
+          <t>In 'Chart Data' sheet:
+A1: Severity, B1: Count
+A2: Critical  B2: =COUNTIF(BugTracker!C:C,"Critical")
+A3: High      B3: =COUNTIF(BugTracker!C:C,"High")
+Repeat for Medium and Low</t>
+        </is>
+      </c>
+      <c r="D21" s="57">
+        <f>COUNTIF('Bug Tracker'!C:C,"Critical")</f>
+        <v/>
+      </c>
+      <c r="E21" s="109" t="inlineStr">
+        <is>
+          <t>Bug severity counts ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="108" t="inlineStr">
+        <is>
+          <t>Step 8</t>
+        </is>
+      </c>
+      <c r="B22" s="52" t="inlineStr">
+        <is>
+          <t>Count Bugs by Status</t>
+        </is>
+      </c>
+      <c r="C22" s="58" t="inlineStr">
+        <is>
+          <t>D1: Status, E1: Count
+D2: Open     E2: =COUNTIF('Bug Tracker'!D:D,"Open")
+Repeat for In Progress, Fixed, Verified, Closed, Reopened
+This powers your status donut/pie chart</t>
+        </is>
+      </c>
+      <c r="D22" s="57">
+        <f>COUNTIF('Bug Tracker'!D:D,"Open")</f>
+        <v/>
+      </c>
+      <c r="E22" s="109" t="inlineStr">
+        <is>
+          <t>Status distribution ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="108" t="inlineStr">
+        <is>
+          <t>Step 9</t>
+        </is>
+      </c>
+      <c r="B23" s="52" t="inlineStr">
+        <is>
+          <t>Bugs per Module</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>G1: Module, H1: Count
+List each module name in G2:G11
+H2: =COUNTIF('Bug Tracker'!E:E, G2)
+Copy down — shows which module has the most bugs (hotspot!)</t>
+        </is>
+      </c>
+      <c r="D23" s="57">
+        <f>COUNTIF('Bug Tracker'!E:E,G2)</f>
+        <v/>
+      </c>
+      <c r="E23" s="109" t="inlineStr">
+        <is>
+          <t>Module hotspots found ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="108" t="inlineStr">
+        <is>
+          <t>Step 10</t>
+        </is>
+      </c>
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>Monthly Bug Trend</t>
+        </is>
+      </c>
+      <c r="C24" s="58" t="inlineStr">
+        <is>
+          <t>P1: Month, Q1: Bugs Opened
+List months: Oct 2025, Nov 2025... May 2026
+Use COUNTIFS with MONTH() and YEAR() functions:
+=COUNTIFS(MONTH('Bug Tracker'!H:H),10, YEAR('Bug Tracker'!H:H),2025)
+Or use TEXT: =COUNTIF(TEXT('Bug Tracker'!H:H,"MMM YYYY"),P2)</t>
+        </is>
+      </c>
+      <c r="D24" s="57">
+        <f>COUNTIFS(MONTH('Bug Tracker'!H:H),10,YEAR('Bug Tracker'!H:H),2025)</f>
+        <v/>
+      </c>
+      <c r="E24" s="109" t="inlineStr">
+        <is>
+          <t>Monthly trend ready ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="108" t="inlineStr">
+        <is>
+          <t>Step 11</t>
+        </is>
+      </c>
+      <c r="B25" s="52" t="inlineStr">
+        <is>
+          <t>Defect Removal Efficiency (DRE)</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>DRE = Bugs Closed / Total Bugs per Sprint × 100
+S1: Sprint, T1: DRE %
+T2: =COUNTIFS('Bug Tracker'!G:G,S2,'Bug Tracker'!D:D,"Closed")/COUNTIF('Bug Tracker'!G:G,S2)*100</t>
+        </is>
+      </c>
+      <c r="D25" s="57">
+        <f>COUNTIFS('Bug Tracker'!G:G,S2,'Bug Tracker'!D:D,"Closed")/COUNTIF('Bug Tracker'!G:G,S2)*100</f>
+        <v/>
+      </c>
+      <c r="E25" s="109" t="inlineStr">
+        <is>
+          <t>DRE per sprint ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t>💡 TIP: Always build a separate 'Chart Data' sheet that holds only summary numbers. Charts linked to clean summary tables are faster, easier to debug, and won't break when raw data changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="111" t="inlineStr">
+        <is>
+          <t>PHASE 3: CREATE THE MAIN DASHBOARD PAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="108" t="inlineStr">
+        <is>
+          <t>Step 12</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="inlineStr">
+        <is>
+          <t>Dark Theme Dashboard</t>
         </is>
       </c>
       <c r="C29" s="37" t="inlineStr">
         <is>
-          <t>Apply Percentage format instantly</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="74" t="inlineStr">
-        <is>
-          <t>Ctrl + Shift + #</t>
-        </is>
-      </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>Apply Date format instantly</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="75" t="inlineStr">
-        <is>
-          <t>Alt + H + H</t>
+          <t>Create sheet '🎯 QA Dashboard'
+View → uncheck Gridlines
+Select ALL cells (Ctrl+A) → Fill color: #0D1117 (dark gray-black)
+Set all font color to white — dark theme dashboards look very professional!</t>
+        </is>
+      </c>
+      <c r="D29" s="57" t="inlineStr"/>
+      <c r="E29" s="109" t="inlineStr">
+        <is>
+          <t>Dark theme applied ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="108" t="inlineStr">
+        <is>
+          <t>Step 13</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="inlineStr">
+        <is>
+          <t>Title Banner with Accent Bar</t>
+        </is>
+      </c>
+      <c r="C30" s="64" t="inlineStr">
+        <is>
+          <t>Merge A1:N1, height 50, size 20 bold white text
+Row 2: fill with a bright accent color (blue/red/orange) height=4
+This creates a thin color bar under the title — a modern design trick!
+Row 3: subtitle row with project name, date, total counts</t>
+        </is>
+      </c>
+      <c r="D30" s="57" t="inlineStr"/>
+      <c r="E30" s="109" t="inlineStr">
+        <is>
+          <t>Title banner created ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="108" t="inlineStr">
+        <is>
+          <t>Step 14</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="inlineStr">
+        <is>
+          <t>6 KPI Cards</t>
         </is>
       </c>
       <c r="C31" s="37" t="inlineStr">
         <is>
-          <t>Open cell background color picker</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="74" t="inlineStr">
-        <is>
-          <t>Ctrl + Shift + C/V</t>
-        </is>
-      </c>
-      <c r="C32" s="33" t="inlineStr">
-        <is>
-          <t>Copy / Paste formatting only (Format Painter via keyboard)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25" customHeight="1">
-      <c r="A34" s="59" t="inlineStr">
-        <is>
-          <t>📊  CHART TRICKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="76" t="inlineStr">
-        <is>
-          <t>Shortcut / Tip</t>
-        </is>
-      </c>
-      <c r="C35" s="76" t="inlineStr">
-        <is>
-          <t>What it Does</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="77" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="C36" s="33" t="inlineStr">
-        <is>
-          <t>Create a chart on a NEW sheet from selected data instantly</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="78" t="inlineStr">
-        <is>
-          <t>Alt + F1</t>
-        </is>
-      </c>
-      <c r="C37" s="37" t="inlineStr">
-        <is>
-          <t>Create a chart EMBEDDED in the current sheet from selected data</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="77" t="inlineStr">
-        <is>
-          <t>Click chart + Delete</t>
-        </is>
-      </c>
-      <c r="C38" s="33" t="inlineStr">
-        <is>
-          <t>Delete a chart quickly</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="78" t="inlineStr">
-        <is>
-          <t>Ctrl + click bars</t>
+          <t>Each card = 2 merged cells stacked:
+  Top cell: large number value (font size 22, bold)
+  Bottom cell: label text (font size 9, caps)
+  Sub-text: context (font size 8, italic, gray)
+Space them across columns B, F, J, N, R, V
+Give each card a different accent color background</t>
+        </is>
+      </c>
+      <c r="D31" s="57">
+        <f>COUNTIF('Bug Tracker'!D:D,"Open")+COUNTIF('Bug Tracker'!D:D,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="E31" s="109" t="inlineStr">
+        <is>
+          <t>KPI row complete ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="108" t="inlineStr">
+        <is>
+          <t>Step 15</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="inlineStr">
+        <is>
+          <t>Critical Bug KPI (Alert Style)</t>
+        </is>
+      </c>
+      <c r="C32" s="64" t="inlineStr">
+        <is>
+          <t>For the 'Critical Open' KPI card:
+Formula: =COUNTIFS('Bug Tracker'!C:C,"Critical",'Bug Tracker'!D:D,"Open")
+Set background to deep red: #2D0A0A
+This visually signals DANGER vs the other cards' neutral colors</t>
+        </is>
+      </c>
+      <c r="D32" s="57">
+        <f>COUNTIFS('Bug Tracker'!C:C,"Critical",'Bug Tracker'!D:D,"Open")</f>
+        <v/>
+      </c>
+      <c r="E32" s="109" t="inlineStr">
+        <is>
+          <t>Alert KPI card ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="108" t="inlineStr">
+        <is>
+          <t>Step 16</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="inlineStr">
+        <is>
+          <t>Insert 6 Charts from Chart Data sheet</t>
+        </is>
+      </c>
+      <c r="C33" s="37" t="inlineStr">
+        <is>
+          <t>Chart 1: Severity → Pie chart (A1:B5)
+Chart 2: Status → Column chart (D1:E7)
+Chart 3: Module bugs → Horizontal Bar (G1:H11)
+Chart 4: Sprint tests → Stacked Column (J1:M9)
+Chart 5: Monthly trend → Line chart (P1:Q9)
+Chart 6: DRE % → Line chart (S1:T9)
+Arrange in 2×3 grid on the dashboard</t>
+        </is>
+      </c>
+      <c r="D33" s="57" t="inlineStr"/>
+      <c r="E33" s="109" t="inlineStr">
+        <is>
+          <t>6 charts arranged ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="108" t="inlineStr">
+        <is>
+          <t>Step 17</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="inlineStr">
+        <is>
+          <t>Critical Bugs Alert Table</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>At the bottom of the dashboard:
+Create a table showing only Open + Critical/High bugs
+Use FILTER function (Excel 365): =FILTER(BugTable, (Status='Open')*(Severity='Critical'))
+OR manually sort Bug Tracker by Severity → copy top 10 to dashboard
+Add red header row — this becomes the 'action items' section</t>
+        </is>
+      </c>
+      <c r="D34" s="57">
+        <f>FILTER('Bug Tracker'!A:J,('Bug Tracker'!D:D="Open")*('Bug Tracker'!C:C="Critical"))</f>
+        <v/>
+      </c>
+      <c r="E34" s="109" t="inlineStr">
+        <is>
+          <t>Action items table ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="55" t="inlineStr">
+        <is>
+          <t>💡 TIP: For the dark theme: select all cells (Ctrl+A), set fill to #0D1117 and font to white BEFORE adding content. It's much easier than changing cells one by one!</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="59" t="inlineStr">
+        <is>
+          <t>PHASE 4: TESTER SCORECARD + SPRINT HEALTH SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="108" t="inlineStr">
+        <is>
+          <t>Step 18</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="inlineStr">
+        <is>
+          <t>Tester Close Rate Formula</t>
+        </is>
+      </c>
+      <c r="C38" s="60" t="inlineStr">
+        <is>
+          <t>For each tester in column B:
+Bugs Assigned: =COUNTIF('Bug Tracker'!F:F, B2)
+Bugs Closed:   =COUNTIFS('Bug Tracker'!F:F,B2,'Bug Tracker'!D:D,"Closed")
+Close Rate %:  =D2/C2*100</t>
+        </is>
+      </c>
+      <c r="D38" s="57">
+        <f>COUNTIFS('Bug Tracker'!F:F,B2,'Bug Tracker'!D:D,"Closed")/COUNTIF('Bug Tracker'!F:F,B2)*100</f>
+        <v/>
+      </c>
+      <c r="E38" s="109" t="inlineStr">
+        <is>
+          <t>Performance % calculated ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="108" t="inlineStr">
+        <is>
+          <t>Step 19</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="inlineStr">
+        <is>
+          <t>Data Bars on Close Rate</t>
         </is>
       </c>
       <c r="C39" s="37" t="inlineStr">
         <is>
-          <t>Select one specific bar/slice to format individually</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="77" t="inlineStr">
-        <is>
-          <t>Double-click axis</t>
-        </is>
-      </c>
-      <c r="C40" s="33" t="inlineStr">
-        <is>
-          <t>Open Format Axis panel</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="78" t="inlineStr">
-        <is>
-          <t>Right-click → Select Data</t>
+          <t>Select Close Rate column
+Home → Conditional Formatting → Data Bars → choose a color
+The bar fills wider as the % increases
+You instantly see who's closing the most bugs — no chart needed!</t>
+        </is>
+      </c>
+      <c r="D39" s="57" t="inlineStr"/>
+      <c r="E39" s="109" t="inlineStr">
+        <is>
+          <t>Data bars applied ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="108" t="inlineStr">
+        <is>
+          <t>Step 20</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="inlineStr">
+        <is>
+          <t>Performance Label with IFS</t>
+        </is>
+      </c>
+      <c r="C40" s="60" t="inlineStr">
+        <is>
+          <t>Add a 'Performance' column:
+=IFS(F2&gt;=75,"🥇 Excellent",F2&gt;=60,"🥈 Good",F2&gt;=45,"🥉 Average",TRUE,"⚠️ Needs Improvement")
+Use conditional formatting to color:  green/blue/yellow/red</t>
+        </is>
+      </c>
+      <c r="D40" s="57">
+        <f>IFS(F2&gt;=75,"🥇 Excellent",F2&gt;=60,"🥈 Good",F2&gt;=45,"🥉 Average",TRUE,"⚠️ Needs Improvement")</f>
+        <v/>
+      </c>
+      <c r="E40" s="109" t="inlineStr">
+        <is>
+          <t>Emoji labels added ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="108" t="inlineStr">
+        <is>
+          <t>Step 21</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="inlineStr">
+        <is>
+          <t>Sprint Health Score</t>
         </is>
       </c>
       <c r="C41" s="37" t="inlineStr">
         <is>
-          <t>Change what data the chart uses</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="25" customHeight="1">
-      <c r="A43" s="63" t="inlineStr">
-        <is>
-          <t>💡  DASHBOARD BEST PRACTICES</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="79" t="inlineStr">
-        <is>
-          <t>Shortcut / Tip</t>
-        </is>
-      </c>
-      <c r="C44" s="79" t="inlineStr">
-        <is>
-          <t>What it Does</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="80" t="inlineStr">
-        <is>
-          <t>Use consistent colors</t>
-        </is>
-      </c>
-      <c r="C45" s="33" t="inlineStr">
-        <is>
-          <t>Pick 2-3 main colors and stick to them throughout</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="81" t="inlineStr">
-        <is>
-          <t>Align everything</t>
-        </is>
-      </c>
-      <c r="C46" s="37" t="inlineStr">
-        <is>
-          <t>Charts and tables should align to cell grid (hold Alt while resizing)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="80" t="inlineStr">
-        <is>
-          <t>Less is more</t>
-        </is>
-      </c>
-      <c r="C47" s="33" t="inlineStr">
-        <is>
-          <t>Don't add every possible chart — 4-6 visuals max per dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="81" t="inlineStr">
-        <is>
-          <t>Add a title section</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>Every dashboard needs a clear title + date/source information</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="80" t="inlineStr">
-        <is>
-          <t>Use named ranges</t>
-        </is>
-      </c>
-      <c r="C49" s="33" t="inlineStr">
-        <is>
-          <t>Name your key data ranges (Ctrl+F3) for cleaner formulas</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="81" t="inlineStr">
-        <is>
-          <t>Protect your summary sheets</t>
-        </is>
-      </c>
-      <c r="C50" s="37" t="inlineStr">
-        <is>
-          <t>Review tab → Protect Sheet so formula cells can't be broken</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="80" t="inlineStr">
-        <is>
-          <t>Test responsiveness</t>
-        </is>
-      </c>
-      <c r="C51" s="33" t="inlineStr">
-        <is>
-          <t>Click slicers/filters to verify all charts update correctly</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="81" t="inlineStr">
-        <is>
-          <t>Save as .xlsx</t>
-        </is>
-      </c>
-      <c r="C52" s="37" t="inlineStr">
-        <is>
-          <t>Always save as .xlsx to preserve charts, formatting &amp; macros</t>
+          <t>Health = weighted average of Pass Rate and DRE:
+=PassRate*0.5 + DRE*0.5
+Then use IFS:
+=IFS(Score&gt;=75,"🟢 Healthy",Score&gt;=55,"🟡 At Risk",TRUE,"🔴 Critical")
+This gives a single-glance verdict for each sprint</t>
+        </is>
+      </c>
+      <c r="D41" s="57">
+        <f>(F2*0.5)+(M2*0.5)</f>
+        <v/>
+      </c>
+      <c r="E41" s="109" t="inlineStr">
+        <is>
+          <t>Health score calculated ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="108" t="inlineStr">
+        <is>
+          <t>Step 22</t>
+        </is>
+      </c>
+      <c r="B42" s="52" t="inlineStr">
+        <is>
+          <t>Freeze Header Row on All Sheets</t>
+        </is>
+      </c>
+      <c r="C42" s="60" t="inlineStr">
+        <is>
+          <t>On every sheet with data:
+Click cell A2 (below header)
+View tab → Freeze Panes → Freeze Top Row
+Now when you scroll down through 200 bugs, headers stay visible!</t>
+        </is>
+      </c>
+      <c r="D42" s="57" t="inlineStr"/>
+      <c r="E42" s="109" t="inlineStr">
+        <is>
+          <t>Headers frozen ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="108" t="inlineStr">
+        <is>
+          <t>Step 23</t>
+        </is>
+      </c>
+      <c r="B43" s="52" t="inlineStr">
+        <is>
+          <t>Protect Formula Cells</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="inlineStr">
+        <is>
+          <t>On the Chart Data sheet (all formulas):
+Ctrl+A → Format Cells → Protection → check 'Locked'
+Review tab → Protect Sheet → OK
+Now nobody can accidentally break the formulas that feed the dashboard</t>
+        </is>
+      </c>
+      <c r="D43" s="57" t="inlineStr"/>
+      <c r="E43" s="109" t="inlineStr">
+        <is>
+          <t>Formulas protected ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="55" t="inlineStr">
+        <is>
+          <t>💡 TIP: Use emojis (🔴🟡🟢) in cells for status indicators — they show without needing formatting, look great in dark themes, and work in any Excel version!</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="106" t="inlineStr">
+        <is>
+          <t>📌  QA-SPECIFIC EXCEL FORMULAS — QUICK REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="B47" s="112" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C47" s="112" t="inlineStr">
+        <is>
+          <t>Syntax</t>
+        </is>
+      </c>
+      <c r="D47" s="112" t="inlineStr">
+        <is>
+          <t>QA Example</t>
+        </is>
+      </c>
+      <c r="E47" s="112" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="B48" s="113" t="inlineStr">
+        <is>
+          <t>COUNTIF</t>
+        </is>
+      </c>
+      <c r="C48" s="42" t="inlineStr">
+        <is>
+          <t>COUNTIF(range, criteria)</t>
+        </is>
+      </c>
+      <c r="D48" s="43">
+        <f>COUNTIF(D:D,"Open")</f>
+        <v/>
+      </c>
+      <c r="E48" s="33" t="inlineStr">
+        <is>
+          <t>Count all open bugs — core of every QA metric</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="B49" s="114" t="inlineStr">
+        <is>
+          <t>COUNTIFS</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>COUNTIFS(r1,c1,r2,c2,...)</t>
+        </is>
+      </c>
+      <c r="D49" s="41">
+        <f>COUNTIFS(C:C,"Critical",D:D,"Open")</f>
+        <v/>
+      </c>
+      <c r="E49" s="37" t="inlineStr">
+        <is>
+          <t>Count critical AND open bugs simultaneously</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="B50" s="113" t="inlineStr">
+        <is>
+          <t>DATEDIF</t>
+        </is>
+      </c>
+      <c r="C50" s="42" t="inlineStr">
+        <is>
+          <t>DATEDIF(start,end,"D")</t>
+        </is>
+      </c>
+      <c r="D50" s="43">
+        <f>DATEDIF(H2,TODAY(),"D")</f>
+        <v/>
+      </c>
+      <c r="E50" s="33" t="inlineStr">
+        <is>
+          <t>Exact days a bug has been open</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="B51" s="114" t="inlineStr">
+        <is>
+          <t>TODAY</t>
+        </is>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>TODAY()</t>
+        </is>
+      </c>
+      <c r="D51" s="41">
+        <f>IF(D2="Closed",I2-H2,TODAY()-H2)</f>
+        <v/>
+      </c>
+      <c r="E51" s="37" t="inlineStr">
+        <is>
+          <t>Auto-update days open every day without touching the file</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="B52" s="113" t="inlineStr">
+        <is>
+          <t>IFS</t>
+        </is>
+      </c>
+      <c r="C52" s="42" t="inlineStr">
+        <is>
+          <t>IFS(c1,v1,c2,v2,...,TRUE,default)</t>
+        </is>
+      </c>
+      <c r="D52" s="43">
+        <f>IFS(E2&gt;=75,"Excellent",E2&gt;=50,"Good",TRUE,"Poor")</f>
+        <v/>
+      </c>
+      <c r="E52" s="33" t="inlineStr">
+        <is>
+          <t>Assign performance labels based on close rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="B53" s="114" t="inlineStr">
+        <is>
+          <t>FILTER</t>
+        </is>
+      </c>
+      <c r="C53" s="40" t="inlineStr">
+        <is>
+          <t>FILTER(array, include, [empty])</t>
+        </is>
+      </c>
+      <c r="D53" s="41">
+        <f>FILTER(A:J,(D:D="Open")*(C:C="Critical"))</f>
+        <v/>
+      </c>
+      <c r="E53" s="37" t="inlineStr">
+        <is>
+          <t>Show ONLY open critical bugs (Excel 365 / 2021+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="B54" s="113" t="inlineStr">
+        <is>
+          <t>SORT</t>
+        </is>
+      </c>
+      <c r="C54" s="42" t="inlineStr">
+        <is>
+          <t>SORT(array, sort_index, [order])</t>
+        </is>
+      </c>
+      <c r="D54" s="43">
+        <f>SORT(A2:J201,J2:J201,-1)</f>
+        <v/>
+      </c>
+      <c r="E54" s="33" t="inlineStr">
+        <is>
+          <t>Sort bugs by days open (descending) — longest open first</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="B55" s="114" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
+      <c r="C55" s="40" t="inlineStr">
+        <is>
+          <t>UNIQUE(array)</t>
+        </is>
+      </c>
+      <c r="D55" s="41">
+        <f>UNIQUE('Bug Tracker'!E2:E201)</f>
+        <v/>
+      </c>
+      <c r="E55" s="37" t="inlineStr">
+        <is>
+          <t>Get list of all unique modules without duplicates</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="B56" s="113" t="inlineStr">
+        <is>
+          <t>AVERAGEIFS</t>
+        </is>
+      </c>
+      <c r="C56" s="42" t="inlineStr">
+        <is>
+          <t>AVERAGEIFS(avg_r,r1,c1,r2,c2)</t>
+        </is>
+      </c>
+      <c r="D56" s="43">
+        <f>AVERAGEIFS(J:J,D:D,"Open",C:C,"Critical")</f>
+        <v/>
+      </c>
+      <c r="E56" s="33" t="inlineStr">
+        <is>
+          <t>Average days open for critical open bugs only</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="B57" s="114" t="inlineStr">
+        <is>
+          <t>NETWORKDAYS</t>
+        </is>
+      </c>
+      <c r="C57" s="40" t="inlineStr">
+        <is>
+          <t>NETWORKDAYS(start, end)</t>
+        </is>
+      </c>
+      <c r="D57" s="41">
+        <f>NETWORKDAYS(H2,TODAY())</f>
+        <v/>
+      </c>
+      <c r="E57" s="37" t="inlineStr">
+        <is>
+          <t>Count working days open (excludes weekends) — true SLA metric</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="115" t="inlineStr">
+        <is>
+          <t>📝 NOTE: FILTER and SORT are only available in Excel 365 / Excel 2021+. For older versions, use Advanced Filter (Data tab → Advanced) or sort manually.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="D4"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="D35"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="D44"/>
-    <mergeCell ref="D25"/>
-    <mergeCell ref="D13"/>
+  <mergeCells count="25">
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A58:E58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
